--- a/poker/resources/sample/RobotAction_Chess.xlsx
+++ b/poker/resources/sample/RobotAction_Chess.xlsx
@@ -163,19 +163,19 @@
     <t>ID</t>
   </si>
   <si>
-    <t>ActionID</t>
-  </si>
-  <si>
-    <t>GameID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DelayTime </t>
-  </si>
-  <si>
-    <t>WinBetAction</t>
-  </si>
-  <si>
-    <t>FailBetAction</t>
+    <t>actionID</t>
+  </si>
+  <si>
+    <t>gameID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">delayTime </t>
+  </si>
+  <si>
+    <t>winBetAction</t>
+  </si>
+  <si>
+    <t>failBetAction</t>
   </si>
   <si>
     <t>大额下注</t>
@@ -394,12 +394,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1503,7 +1503,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:8">
       <c r="A5">
-        <v>1</v>
+        <v>200001</v>
       </c>
       <c r="B5" s="3">
         <v>20099</v>
@@ -1529,7 +1529,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:8">
       <c r="A6">
-        <v>2</v>
+        <v>200002</v>
       </c>
       <c r="B6" s="3">
         <v>20099</v>
@@ -1555,7 +1555,7 @@
     </row>
     <row r="7" ht="16.5" spans="1:8">
       <c r="A7">
-        <v>3</v>
+        <v>200003</v>
       </c>
       <c r="B7" s="3">
         <v>20099</v>
@@ -1581,7 +1581,7 @@
     </row>
     <row r="8" ht="16.5" spans="1:8">
       <c r="A8">
-        <v>4</v>
+        <v>200004</v>
       </c>
       <c r="B8" s="3">
         <v>20075</v>
@@ -1607,7 +1607,7 @@
     </row>
     <row r="9" ht="16.5" spans="1:8">
       <c r="A9">
-        <v>5</v>
+        <v>200005</v>
       </c>
       <c r="B9" s="3">
         <v>20075</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="10" ht="16.5" spans="1:8">
       <c r="A10">
-        <v>6</v>
+        <v>200006</v>
       </c>
       <c r="B10" s="3">
         <v>20075</v>
@@ -1659,7 +1659,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:8">
       <c r="A11">
-        <v>7</v>
+        <v>200007</v>
       </c>
       <c r="B11" s="3">
         <v>20050</v>
@@ -1685,7 +1685,7 @@
     </row>
     <row r="12" ht="16.5" spans="1:8">
       <c r="A12">
-        <v>8</v>
+        <v>200008</v>
       </c>
       <c r="B12" s="3">
         <v>20050</v>
@@ -1711,7 +1711,7 @@
     </row>
     <row r="13" ht="16.5" spans="1:8">
       <c r="A13">
-        <v>9</v>
+        <v>200009</v>
       </c>
       <c r="B13" s="3">
         <v>20050</v>
@@ -1737,7 +1737,7 @@
     </row>
     <row r="14" ht="16.5" spans="1:8">
       <c r="A14">
-        <v>10</v>
+        <v>200010</v>
       </c>
       <c r="B14" s="3">
         <v>20025</v>
@@ -1763,7 +1763,7 @@
     </row>
     <row r="15" ht="16.5" spans="1:8">
       <c r="A15">
-        <v>11</v>
+        <v>200011</v>
       </c>
       <c r="B15" s="3">
         <v>20025</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="16" ht="16.5" spans="1:8">
       <c r="A16">
-        <v>12</v>
+        <v>200012</v>
       </c>
       <c r="B16" s="3">
         <v>20025</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="17" ht="16.5" spans="1:8">
       <c r="A17">
-        <v>13</v>
+        <v>200013</v>
       </c>
       <c r="B17" s="3">
         <v>20001</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="18" ht="16.5" spans="1:8">
       <c r="A18">
-        <v>14</v>
+        <v>200014</v>
       </c>
       <c r="B18" s="3">
         <v>20001</v>
@@ -1867,7 +1867,7 @@
     </row>
     <row r="19" ht="16.5" spans="1:8">
       <c r="A19">
-        <v>15</v>
+        <v>200015</v>
       </c>
       <c r="B19" s="3">
         <v>20001</v>

--- a/poker/resources/sample/RobotAction_Chess.xlsx
+++ b/poker/resources/sample/RobotAction_Chess.xlsx
@@ -55,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -79,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -97,12 +97,11 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-格式
-{[权重、弃牌][权重、跟注或过][权重、加注1][权重、加注2]……}</t>
+德州游戏中，机器人【加注】权重值乘以此值并除以10000后在参与行为权重随机</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -120,9 +119,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-格式
-{[权重、弃牌][权重、跟注][权重、加注1][权重、加注2]……}
-</t>
+21点游戏中，机器人【要牌】权重值乘以此值并除以10000后在参与行为权重随机</t>
         </r>
       </text>
     </comment>
@@ -131,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="61">
   <si>
     <t>序列</t>
   </si>
@@ -142,22 +139,40 @@
     <t>游戏ID</t>
   </si>
   <si>
-    <t>延迟押注时间</t>
-  </si>
-  <si>
-    <t>获胜时押注筹码</t>
-  </si>
-  <si>
-    <t>失败时押注筹码</t>
+    <t>每次延迟行为时间</t>
+  </si>
+  <si>
+    <t>胜利后行为概率,准备概率_展示牌型</t>
+  </si>
+  <si>
+    <t>失败后行为概率,准备概率_展示牌型</t>
+  </si>
+  <si>
+    <t>德州-加注时大盲筹码倍数权重</t>
+  </si>
+  <si>
+    <t>德州-最后一轮最大牌且加注时Allin概率万分比</t>
+  </si>
+  <si>
+    <t>德州-【加注】权重乘值万分比</t>
+  </si>
+  <si>
+    <t>21点-筹码下注权重(筹码位置_权重）</t>
+  </si>
+  <si>
+    <t>21点-【要牌】权重乘值万分比</t>
   </si>
   <si>
     <t>Int</t>
   </si>
   <si>
-    <t>list&lt;list&lt;int&gt;{,3}&gt;{;}</t>
-  </si>
-  <si>
-    <t>list&lt;list&lt;int&gt;{,2}&gt;{;}</t>
+    <t>list&lt;list&lt;int&gt;{,3}&gt;{|}</t>
+  </si>
+  <si>
+    <t>list&lt;int&gt;{_}</t>
+  </si>
+  <si>
+    <t>map&lt;int{_}int&gt;{|}</t>
   </si>
   <si>
     <t>ID</t>
@@ -172,22 +187,49 @@
     <t xml:space="preserve">delayTime </t>
   </si>
   <si>
-    <t>winBetAction</t>
-  </si>
-  <si>
-    <t>failBetAction</t>
+    <t>continueAfterVictory</t>
+  </si>
+  <si>
+    <t>continueAfterFail</t>
+  </si>
+  <si>
+    <t>addBetMultiple</t>
+  </si>
+  <si>
+    <t>allinWeight</t>
+  </si>
+  <si>
+    <t>addProactiveWeight</t>
+  </si>
+  <si>
+    <t>blackjackBet</t>
+  </si>
+  <si>
+    <t>standWeight</t>
   </si>
   <si>
     <t>大额下注</t>
   </si>
   <si>
+    <t>21点</t>
+  </si>
+  <si>
     <t>21点基础场</t>
   </si>
   <si>
-    <t>70,100,500;30,500,1000</t>
-  </si>
-  <si>
-    <t>10,1;20,2;50,3;50,4;50,5;20,6;10,7</t>
+    <t>70,100,500|30,500,1000</t>
+  </si>
+  <si>
+    <t>10000_8000</t>
+  </si>
+  <si>
+    <t>8000_5000</t>
+  </si>
+  <si>
+    <t>1_3000|2_2000|3_1500|5_1000</t>
+  </si>
+  <si>
+    <t>1_500|2_1000|3_2000|4_4000|5_6000|6_8000|7_10000</t>
   </si>
   <si>
     <t>21点中级场</t>
@@ -199,36 +241,88 @@
     <t>中大额下注</t>
   </si>
   <si>
-    <t>70,500,1000;30,1000,2000</t>
+    <t>70,500,1000|30,1000,2000</t>
+  </si>
+  <si>
+    <t>9500_7500</t>
+  </si>
+  <si>
+    <t>7500_4500</t>
+  </si>
+  <si>
+    <t>1_3000|2_2000|3_1000|5_500</t>
+  </si>
+  <si>
+    <t>1_1000|2_2000|3_4000|4_4000|5_6000|6_6000|7_6000</t>
+  </si>
+  <si>
+    <t>1_4000|2_2000|3_1000|5_500</t>
   </si>
   <si>
     <t>中额下注</t>
   </si>
   <si>
-    <t>70,500,1500;30,1000,2000</t>
+    <t>70,500,1500|30,1000,2000</t>
+  </si>
+  <si>
+    <t>9000_7000</t>
+  </si>
+  <si>
+    <t>7000_4000</t>
+  </si>
+  <si>
+    <t>1_4000|2_2000|3_1000|5_200</t>
+  </si>
+  <si>
+    <t>1_4000|2_4000|3_4000|4_4000|5_4000|6_4000|7_2000</t>
   </si>
   <si>
     <t>中小额下注</t>
   </si>
   <si>
-    <t>70,1000,1500;30,1000,2500</t>
+    <t>70,1000,1500|30,1000,2500</t>
+  </si>
+  <si>
+    <t>8500_6500</t>
+  </si>
+  <si>
+    <t>6500_3500</t>
+  </si>
+  <si>
+    <t>1_5000|2_2000|3_500|5_0</t>
+  </si>
+  <si>
+    <t>1_6000|2_6000|3_6000|4_4000|5_4000|6_2000|7_1000</t>
   </si>
   <si>
     <t>小额下注</t>
   </si>
   <si>
-    <t>70,1500,2500;30,2500,5000</t>
+    <t>70,1500,2500|30,2500,5000</t>
+  </si>
+  <si>
+    <t>8000_6000</t>
+  </si>
+  <si>
+    <t>6000_3000</t>
+  </si>
+  <si>
+    <t>1_10000|2_8000|3_6000|4_4000|5_2000|6_1000|7_500</t>
+  </si>
+  <si>
+    <t>德州</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -394,18 +488,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -427,6 +521,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -724,7 +830,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
@@ -747,7 +853,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -771,16 +877,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -789,89 +895,90 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -879,6 +986,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -894,8 +1004,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -945,6 +1057,7 @@
     <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2 2" xfId="49"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -1419,17 +1532,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:N34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="9.375" customWidth="1"/>
-    <col min="5" max="5" width="11.25" customWidth="1"/>
-    <col min="6" max="6" width="26.625" customWidth="1"/>
-    <col min="7" max="8" width="35.625" customWidth="1"/>
+    <col min="4" max="5" width="9.375" customWidth="1"/>
+    <col min="6" max="6" width="11.25" customWidth="1"/>
+    <col min="7" max="7" width="26.625" customWidth="1"/>
+    <col min="8" max="8" width="30.2916666666667" customWidth="1"/>
+    <col min="9" max="9" width="31.9083333333333" customWidth="1"/>
+    <col min="10" max="10" width="27.6416666666667" customWidth="1"/>
+    <col min="11" max="11" width="14.2583333333333" customWidth="1"/>
+    <col min="12" max="12" width="24.625" customWidth="1"/>
+    <col min="13" max="13" width="44.5583333333333" customWidth="1"/>
+    <col min="14" max="14" width="24.625" customWidth="1"/>
+    <col min="15" max="21" width="6.46666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:8">
+    <row r="1" ht="16.5" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1441,454 +1561,1432 @@
         <v>2</v>
       </c>
       <c r="E1" s="1"/>
-      <c r="F1" t="s">
+      <c r="F1" s="1"/>
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:8">
+      <c r="J1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:14">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" t="s">
-        <v>7</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="F2" s="2"/>
       <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:8">
+        <v>12</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:14">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
+      <c r="F3" s="2"/>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" spans="2:5">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="2:6">
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:8">
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:14">
       <c r="A5">
         <v>200001</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>20099</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="C5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="5">
         <v>30010001</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
+        <v>27</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:8">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5">
+        <v>8000</v>
+      </c>
+      <c r="L5">
+        <v>12000</v>
+      </c>
+      <c r="M5" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:14">
       <c r="A6">
         <v>200002</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="4">
         <v>20099</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="C6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="5">
         <v>30010002</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>17</v>
+      <c r="E6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:8">
+        <v>30</v>
+      </c>
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6">
+        <v>8000</v>
+      </c>
+      <c r="L6">
+        <v>12000</v>
+      </c>
+      <c r="M6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:14">
       <c r="A7">
         <v>200003</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>20099</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="C7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="5">
         <v>30010003</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" t="s">
-        <v>17</v>
+      <c r="E7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:8">
+        <v>30</v>
+      </c>
+      <c r="I7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7">
+        <v>8000</v>
+      </c>
+      <c r="L7">
+        <v>12000</v>
+      </c>
+      <c r="M7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:14">
       <c r="A8">
         <v>200004</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="4">
         <v>20075</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="C8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="5">
         <v>30010001</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" t="s">
-        <v>22</v>
+        <v>27</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8">
+        <v>6000</v>
+      </c>
+      <c r="L8">
+        <v>10000</v>
+      </c>
+      <c r="M8" t="s">
+        <v>41</v>
+      </c>
+      <c r="N8">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:14">
       <c r="A9">
         <v>200005</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>20075</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="4">
+      <c r="C9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="5">
         <v>30010002</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" t="s">
-        <v>22</v>
+      <c r="E9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="G9" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I9" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9">
+        <v>6000</v>
+      </c>
+      <c r="L9">
+        <v>10000</v>
+      </c>
+      <c r="M9" t="s">
+        <v>41</v>
+      </c>
+      <c r="N9">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:14">
       <c r="A10">
         <v>200006</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>20075</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="C10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="5">
         <v>30010003</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" t="s">
-        <v>22</v>
+      <c r="E10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I10" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10">
+        <v>6000</v>
+      </c>
+      <c r="L10">
+        <v>10000</v>
+      </c>
+      <c r="M10" t="s">
+        <v>41</v>
+      </c>
+      <c r="N10">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:14">
       <c r="A11">
         <v>200007</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="4">
         <v>20050</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="4">
+      <c r="C11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="5">
         <v>30010001</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="H11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:8">
+        <v>45</v>
+      </c>
+      <c r="I11" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K11">
+        <v>4000</v>
+      </c>
+      <c r="L11">
+        <v>8000</v>
+      </c>
+      <c r="M11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N11">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:14">
       <c r="A12">
         <v>200008</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="4">
         <v>20050</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="C12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="5">
         <v>30010002</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" t="s">
-        <v>24</v>
+      <c r="E12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:8">
+        <v>45</v>
+      </c>
+      <c r="I12" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" t="s">
+        <v>47</v>
+      </c>
+      <c r="K12">
+        <v>4000</v>
+      </c>
+      <c r="L12">
+        <v>8000</v>
+      </c>
+      <c r="M12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N12">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:14">
       <c r="A13">
         <v>200009</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="4">
         <v>20050</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="4">
+      <c r="C13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="5">
         <v>30010003</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" t="s">
-        <v>24</v>
+      <c r="E13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="H13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:8">
+        <v>45</v>
+      </c>
+      <c r="I13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J13" t="s">
+        <v>47</v>
+      </c>
+      <c r="K13">
+        <v>4000</v>
+      </c>
+      <c r="L13">
+        <v>8000</v>
+      </c>
+      <c r="M13" t="s">
+        <v>48</v>
+      </c>
+      <c r="N13">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:14">
       <c r="A14">
         <v>200010</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="4">
         <v>20025</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="4">
+      <c r="C14" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="5">
         <v>30010001</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="H14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J14" t="s">
+        <v>53</v>
+      </c>
+      <c r="K14">
+        <v>2000</v>
+      </c>
+      <c r="L14">
+        <v>6000</v>
+      </c>
+      <c r="M14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N14">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:14">
       <c r="A15">
         <v>200011</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="4">
         <v>20025</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="4">
+      <c r="C15" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="5">
         <v>30010002</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" t="s">
-        <v>26</v>
+      <c r="E15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="G15" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="H15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I15" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K15">
+        <v>2000</v>
+      </c>
+      <c r="L15">
+        <v>6000</v>
+      </c>
+      <c r="M15" t="s">
+        <v>54</v>
+      </c>
+      <c r="N15">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:14">
       <c r="A16">
         <v>200012</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="4">
         <v>20025</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="4">
+      <c r="C16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="5">
         <v>30010003</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" t="s">
-        <v>26</v>
+      <c r="E16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="G16" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="H16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I16" t="s">
+        <v>52</v>
+      </c>
+      <c r="J16" t="s">
+        <v>53</v>
+      </c>
+      <c r="K16">
+        <v>2000</v>
+      </c>
+      <c r="L16">
+        <v>6000</v>
+      </c>
+      <c r="M16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N16">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:14">
       <c r="A17">
         <v>200013</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="4">
         <v>20001</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="5">
+        <v>30010001</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="4">
-        <v>30010001</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="F17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G17" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="H17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:8">
+        <v>57</v>
+      </c>
+      <c r="I17" t="s">
+        <v>58</v>
+      </c>
+      <c r="J17" t="s">
+        <v>53</v>
+      </c>
+      <c r="K17">
+        <v>1000</v>
+      </c>
+      <c r="L17">
+        <v>4000</v>
+      </c>
+      <c r="M17" t="s">
+        <v>59</v>
+      </c>
+      <c r="N17">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:14">
       <c r="A18">
         <v>200014</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="4">
         <v>20001</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="5">
+        <v>30010002</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="4">
-        <v>30010002</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" t="s">
-        <v>28</v>
+      <c r="F18" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="G18" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="H18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:8">
+        <v>57</v>
+      </c>
+      <c r="I18" t="s">
+        <v>58</v>
+      </c>
+      <c r="J18" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18">
+        <v>1000</v>
+      </c>
+      <c r="L18">
+        <v>4000</v>
+      </c>
+      <c r="M18" t="s">
+        <v>59</v>
+      </c>
+      <c r="N18">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:14">
       <c r="A19">
         <v>200015</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="4">
         <v>20001</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="5">
+        <v>30010003</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="4">
-        <v>30010003</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="F19" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" t="s">
+        <v>57</v>
+      </c>
+      <c r="I19" t="s">
+        <v>58</v>
+      </c>
+      <c r="J19" t="s">
+        <v>53</v>
+      </c>
+      <c r="K19">
+        <v>1000</v>
+      </c>
+      <c r="L19">
+        <v>4000</v>
+      </c>
+      <c r="M19" t="s">
+        <v>59</v>
+      </c>
+      <c r="N19">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A20">
+        <v>200016</v>
+      </c>
+      <c r="B20" s="4">
+        <v>20099</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="5">
+        <v>30020001</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H19" t="s">
-        <v>18</v>
+      <c r="G20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20">
+        <v>8000</v>
+      </c>
+      <c r="L20">
+        <v>12000</v>
+      </c>
+      <c r="M20" t="s">
+        <v>33</v>
+      </c>
+      <c r="N20">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A21">
+        <v>200017</v>
+      </c>
+      <c r="B21" s="4">
+        <v>20099</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="5">
+        <v>30020002</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21">
+        <v>8000</v>
+      </c>
+      <c r="L21">
+        <v>12000</v>
+      </c>
+      <c r="M21" t="s">
+        <v>33</v>
+      </c>
+      <c r="N21">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A22">
+        <v>200018</v>
+      </c>
+      <c r="B22" s="4">
+        <v>20099</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="5">
+        <v>30020003</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" t="s">
+        <v>31</v>
+      </c>
+      <c r="J22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22">
+        <v>8000</v>
+      </c>
+      <c r="L22">
+        <v>12000</v>
+      </c>
+      <c r="M22" t="s">
+        <v>33</v>
+      </c>
+      <c r="N22">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A23">
+        <v>200019</v>
+      </c>
+      <c r="B23" s="4">
+        <v>20075</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="5">
+        <v>30020001</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G23" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" t="s">
+        <v>38</v>
+      </c>
+      <c r="I23" t="s">
+        <v>39</v>
+      </c>
+      <c r="J23" t="s">
+        <v>40</v>
+      </c>
+      <c r="K23">
+        <v>6000</v>
+      </c>
+      <c r="L23">
+        <v>10000</v>
+      </c>
+      <c r="M23" t="s">
+        <v>41</v>
+      </c>
+      <c r="N23">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A24">
+        <v>200020</v>
+      </c>
+      <c r="B24" s="4">
+        <v>20075</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="5">
+        <v>30020002</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24" t="s">
+        <v>38</v>
+      </c>
+      <c r="I24" t="s">
+        <v>39</v>
+      </c>
+      <c r="J24" t="s">
+        <v>42</v>
+      </c>
+      <c r="K24">
+        <v>6000</v>
+      </c>
+      <c r="L24">
+        <v>10000</v>
+      </c>
+      <c r="M24" t="s">
+        <v>41</v>
+      </c>
+      <c r="N24">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A25">
+        <v>200021</v>
+      </c>
+      <c r="B25" s="4">
+        <v>20075</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="5">
+        <v>30020003</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" t="s">
+        <v>37</v>
+      </c>
+      <c r="H25" t="s">
+        <v>38</v>
+      </c>
+      <c r="I25" t="s">
+        <v>39</v>
+      </c>
+      <c r="J25" t="s">
+        <v>42</v>
+      </c>
+      <c r="K25">
+        <v>6000</v>
+      </c>
+      <c r="L25">
+        <v>10000</v>
+      </c>
+      <c r="M25" t="s">
+        <v>41</v>
+      </c>
+      <c r="N25">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A26">
+        <v>200022</v>
+      </c>
+      <c r="B26" s="4">
+        <v>20050</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="5">
+        <v>30020001</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" t="s">
+        <v>44</v>
+      </c>
+      <c r="H26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K26">
+        <v>4000</v>
+      </c>
+      <c r="L26">
+        <v>8000</v>
+      </c>
+      <c r="M26" t="s">
+        <v>48</v>
+      </c>
+      <c r="N26">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A27">
+        <v>200023</v>
+      </c>
+      <c r="B27" s="4">
+        <v>20050</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="5">
+        <v>30020002</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G27" t="s">
+        <v>44</v>
+      </c>
+      <c r="H27" t="s">
+        <v>45</v>
+      </c>
+      <c r="I27" t="s">
+        <v>46</v>
+      </c>
+      <c r="J27" t="s">
+        <v>47</v>
+      </c>
+      <c r="K27">
+        <v>4000</v>
+      </c>
+      <c r="L27">
+        <v>8000</v>
+      </c>
+      <c r="M27" t="s">
+        <v>48</v>
+      </c>
+      <c r="N27">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A28">
+        <v>200024</v>
+      </c>
+      <c r="B28" s="4">
+        <v>20050</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="5">
+        <v>30020003</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G28" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" t="s">
+        <v>45</v>
+      </c>
+      <c r="I28" t="s">
+        <v>46</v>
+      </c>
+      <c r="J28" t="s">
+        <v>47</v>
+      </c>
+      <c r="K28">
+        <v>4000</v>
+      </c>
+      <c r="L28">
+        <v>8000</v>
+      </c>
+      <c r="M28" t="s">
+        <v>48</v>
+      </c>
+      <c r="N28">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A29">
+        <v>200025</v>
+      </c>
+      <c r="B29" s="4">
+        <v>20025</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="5">
+        <v>30020001</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" t="s">
+        <v>50</v>
+      </c>
+      <c r="H29" t="s">
+        <v>51</v>
+      </c>
+      <c r="I29" t="s">
+        <v>52</v>
+      </c>
+      <c r="J29" t="s">
+        <v>53</v>
+      </c>
+      <c r="K29">
+        <v>2000</v>
+      </c>
+      <c r="L29">
+        <v>6000</v>
+      </c>
+      <c r="M29" t="s">
+        <v>54</v>
+      </c>
+      <c r="N29">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A30">
+        <v>200026</v>
+      </c>
+      <c r="B30" s="4">
+        <v>20025</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="5">
+        <v>30020002</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G30" t="s">
+        <v>50</v>
+      </c>
+      <c r="H30" t="s">
+        <v>51</v>
+      </c>
+      <c r="I30" t="s">
+        <v>52</v>
+      </c>
+      <c r="J30" t="s">
+        <v>53</v>
+      </c>
+      <c r="K30">
+        <v>2000</v>
+      </c>
+      <c r="L30">
+        <v>6000</v>
+      </c>
+      <c r="M30" t="s">
+        <v>54</v>
+      </c>
+      <c r="N30">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A31">
+        <v>200027</v>
+      </c>
+      <c r="B31" s="4">
+        <v>20025</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="5">
+        <v>30020003</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G31" t="s">
+        <v>50</v>
+      </c>
+      <c r="H31" t="s">
+        <v>51</v>
+      </c>
+      <c r="I31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J31" t="s">
+        <v>53</v>
+      </c>
+      <c r="K31">
+        <v>2000</v>
+      </c>
+      <c r="L31">
+        <v>6000</v>
+      </c>
+      <c r="M31" t="s">
+        <v>54</v>
+      </c>
+      <c r="N31">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A32">
+        <v>200028</v>
+      </c>
+      <c r="B32" s="4">
+        <v>20001</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="5">
+        <v>30020001</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G32" t="s">
+        <v>56</v>
+      </c>
+      <c r="H32" t="s">
+        <v>57</v>
+      </c>
+      <c r="I32" t="s">
+        <v>58</v>
+      </c>
+      <c r="J32" t="s">
+        <v>53</v>
+      </c>
+      <c r="K32">
+        <v>1000</v>
+      </c>
+      <c r="L32">
+        <v>4000</v>
+      </c>
+      <c r="M32" t="s">
+        <v>59</v>
+      </c>
+      <c r="N32">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A33">
+        <v>200029</v>
+      </c>
+      <c r="B33" s="4">
+        <v>20001</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="5">
+        <v>30020002</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G33" t="s">
+        <v>56</v>
+      </c>
+      <c r="H33" t="s">
+        <v>57</v>
+      </c>
+      <c r="I33" t="s">
+        <v>58</v>
+      </c>
+      <c r="J33" t="s">
+        <v>53</v>
+      </c>
+      <c r="K33">
+        <v>1000</v>
+      </c>
+      <c r="L33">
+        <v>4000</v>
+      </c>
+      <c r="M33" t="s">
+        <v>59</v>
+      </c>
+      <c r="N33">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A34">
+        <v>200030</v>
+      </c>
+      <c r="B34" s="4">
+        <v>20001</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="5">
+        <v>30020003</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G34" t="s">
+        <v>56</v>
+      </c>
+      <c r="H34" t="s">
+        <v>57</v>
+      </c>
+      <c r="I34" t="s">
+        <v>58</v>
+      </c>
+      <c r="J34" t="s">
+        <v>53</v>
+      </c>
+      <c r="K34">
+        <v>1000</v>
+      </c>
+      <c r="L34">
+        <v>4000</v>
+      </c>
+      <c r="M34" t="s">
+        <v>59</v>
+      </c>
+      <c r="N34">
+        <v>4000</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/RobotAction_Chess.xlsx
+++ b/poker/resources/sample/RobotAction_Chess.xlsx
@@ -1680,7 +1680,7 @@
         <v>26</v>
       </c>
       <c r="D5" s="5">
-        <v>30010001</v>
+        <v>3001001</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>27</v>
@@ -1724,7 +1724,7 @@
         <v>26</v>
       </c>
       <c r="D6" s="5">
-        <v>30010002</v>
+        <v>3001002</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>27</v>
@@ -1768,7 +1768,7 @@
         <v>26</v>
       </c>
       <c r="D7" s="5">
-        <v>30010003</v>
+        <v>3001003</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>27</v>
@@ -1812,7 +1812,7 @@
         <v>36</v>
       </c>
       <c r="D8" s="5">
-        <v>30010001</v>
+        <v>3001001</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>27</v>
@@ -1856,7 +1856,7 @@
         <v>36</v>
       </c>
       <c r="D9" s="5">
-        <v>30010002</v>
+        <v>3001002</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>27</v>
@@ -1900,7 +1900,7 @@
         <v>36</v>
       </c>
       <c r="D10" s="5">
-        <v>30010003</v>
+        <v>3001003</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>27</v>
@@ -1944,7 +1944,7 @@
         <v>43</v>
       </c>
       <c r="D11" s="5">
-        <v>30010001</v>
+        <v>3001001</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>27</v>
@@ -1988,7 +1988,7 @@
         <v>43</v>
       </c>
       <c r="D12" s="5">
-        <v>30010002</v>
+        <v>3001002</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>27</v>
@@ -2032,7 +2032,7 @@
         <v>43</v>
       </c>
       <c r="D13" s="5">
-        <v>30010003</v>
+        <v>3001003</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>27</v>
@@ -2076,7 +2076,7 @@
         <v>49</v>
       </c>
       <c r="D14" s="5">
-        <v>30010001</v>
+        <v>3001001</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>27</v>
@@ -2120,7 +2120,7 @@
         <v>49</v>
       </c>
       <c r="D15" s="5">
-        <v>30010002</v>
+        <v>3001002</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>27</v>
@@ -2164,7 +2164,7 @@
         <v>49</v>
       </c>
       <c r="D16" s="5">
-        <v>30010003</v>
+        <v>3001003</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>27</v>
@@ -2208,7 +2208,7 @@
         <v>55</v>
       </c>
       <c r="D17" s="5">
-        <v>30010001</v>
+        <v>3001001</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>27</v>
@@ -2252,7 +2252,7 @@
         <v>55</v>
       </c>
       <c r="D18" s="5">
-        <v>30010002</v>
+        <v>3001002</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>27</v>
@@ -2296,7 +2296,7 @@
         <v>55</v>
       </c>
       <c r="D19" s="5">
-        <v>30010003</v>
+        <v>3001003</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>27</v>
@@ -2340,7 +2340,7 @@
         <v>26</v>
       </c>
       <c r="D20" s="5">
-        <v>30020001</v>
+        <v>3002001</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>60</v>
@@ -2384,7 +2384,7 @@
         <v>26</v>
       </c>
       <c r="D21" s="5">
-        <v>30020002</v>
+        <v>3002002</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>60</v>
@@ -2428,7 +2428,7 @@
         <v>26</v>
       </c>
       <c r="D22" s="5">
-        <v>30020003</v>
+        <v>3002003</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>60</v>
@@ -2472,7 +2472,7 @@
         <v>36</v>
       </c>
       <c r="D23" s="5">
-        <v>30020001</v>
+        <v>3002001</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>60</v>
@@ -2516,7 +2516,7 @@
         <v>36</v>
       </c>
       <c r="D24" s="5">
-        <v>30020002</v>
+        <v>3002002</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>60</v>
@@ -2560,7 +2560,7 @@
         <v>36</v>
       </c>
       <c r="D25" s="5">
-        <v>30020003</v>
+        <v>3002003</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>60</v>
@@ -2604,7 +2604,7 @@
         <v>43</v>
       </c>
       <c r="D26" s="5">
-        <v>30020001</v>
+        <v>3002001</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>60</v>
@@ -2648,7 +2648,7 @@
         <v>43</v>
       </c>
       <c r="D27" s="5">
-        <v>30020002</v>
+        <v>3002002</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>60</v>
@@ -2692,7 +2692,7 @@
         <v>43</v>
       </c>
       <c r="D28" s="5">
-        <v>30020003</v>
+        <v>3002003</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>60</v>
@@ -2736,7 +2736,7 @@
         <v>49</v>
       </c>
       <c r="D29" s="5">
-        <v>30020001</v>
+        <v>3002001</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>60</v>
@@ -2780,7 +2780,7 @@
         <v>49</v>
       </c>
       <c r="D30" s="5">
-        <v>30020002</v>
+        <v>3002002</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>60</v>
@@ -2824,7 +2824,7 @@
         <v>49</v>
       </c>
       <c r="D31" s="5">
-        <v>30020003</v>
+        <v>3002003</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>60</v>
@@ -2868,7 +2868,7 @@
         <v>55</v>
       </c>
       <c r="D32" s="5">
-        <v>30020001</v>
+        <v>3002001</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>60</v>
@@ -2912,7 +2912,7 @@
         <v>55</v>
       </c>
       <c r="D33" s="5">
-        <v>30020002</v>
+        <v>3002002</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>60</v>
@@ -2956,7 +2956,7 @@
         <v>55</v>
       </c>
       <c r="D34" s="5">
-        <v>30020003</v>
+        <v>3002003</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>60</v>

--- a/poker/resources/sample/RobotAction_Chess.xlsx
+++ b/poker/resources/sample/RobotAction_Chess.xlsx
@@ -79,6 +79,28 @@
         </r>
       </text>
     </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+游戏开始时，服务器踢出没有准备的机器人</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="L1" authorId="0">
       <text>
         <r>
@@ -128,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="58">
   <si>
     <t>序列</t>
   </si>
@@ -217,7 +239,7 @@
     <t>21点基础场</t>
   </si>
   <si>
-    <t>70,100,500|30,500,1000</t>
+    <t>70,2000,4000|30,1500,2500</t>
   </si>
   <si>
     <t>10000_8000</t>
@@ -241,9 +263,6 @@
     <t>中大额下注</t>
   </si>
   <si>
-    <t>70,500,1000|30,1000,2000</t>
-  </si>
-  <si>
     <t>9500_7500</t>
   </si>
   <si>
@@ -262,7 +281,7 @@
     <t>中额下注</t>
   </si>
   <si>
-    <t>70,500,1500|30,1000,2000</t>
+    <t>70,3000,5000|30,1500,3000</t>
   </si>
   <si>
     <t>9000_7000</t>
@@ -280,9 +299,6 @@
     <t>中小额下注</t>
   </si>
   <si>
-    <t>70,1000,1500|30,1000,2500</t>
-  </si>
-  <si>
     <t>8500_6500</t>
   </si>
   <si>
@@ -296,9 +312,6 @@
   </si>
   <si>
     <t>小额下注</t>
-  </si>
-  <si>
-    <t>70,1500,2500|30,2500,5000</t>
   </si>
   <si>
     <t>8000_6000</t>
@@ -1821,16 +1834,16 @@
         <v>28</v>
       </c>
       <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" t="s">
         <v>37</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>38</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>39</v>
-      </c>
-      <c r="J8" t="s">
-        <v>40</v>
       </c>
       <c r="K8">
         <v>6000</v>
@@ -1839,7 +1852,7 @@
         <v>10000</v>
       </c>
       <c r="M8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N8">
         <v>10000</v>
@@ -1865,16 +1878,16 @@
         <v>34</v>
       </c>
       <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
         <v>37</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>38</v>
       </c>
-      <c r="I9" t="s">
-        <v>39</v>
-      </c>
       <c r="J9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K9">
         <v>6000</v>
@@ -1883,7 +1896,7 @@
         <v>10000</v>
       </c>
       <c r="M9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N9">
         <v>10000</v>
@@ -1909,16 +1922,16 @@
         <v>35</v>
       </c>
       <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" t="s">
         <v>37</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>38</v>
       </c>
-      <c r="I10" t="s">
-        <v>39</v>
-      </c>
       <c r="J10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K10">
         <v>6000</v>
@@ -1927,7 +1940,7 @@
         <v>10000</v>
       </c>
       <c r="M10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N10">
         <v>10000</v>
@@ -1941,7 +1954,7 @@
         <v>20050</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" s="5">
         <v>3001001</v>
@@ -1953,16 +1966,16 @@
         <v>28</v>
       </c>
       <c r="G11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" t="s">
         <v>44</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>45</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>46</v>
-      </c>
-      <c r="J11" t="s">
-        <v>47</v>
       </c>
       <c r="K11">
         <v>4000</v>
@@ -1971,7 +1984,7 @@
         <v>8000</v>
       </c>
       <c r="M11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N11">
         <v>8000</v>
@@ -1985,7 +1998,7 @@
         <v>20050</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D12" s="5">
         <v>3001002</v>
@@ -1997,16 +2010,16 @@
         <v>34</v>
       </c>
       <c r="G12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" t="s">
         <v>44</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>45</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>46</v>
-      </c>
-      <c r="J12" t="s">
-        <v>47</v>
       </c>
       <c r="K12">
         <v>4000</v>
@@ -2015,7 +2028,7 @@
         <v>8000</v>
       </c>
       <c r="M12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N12">
         <v>8000</v>
@@ -2029,7 +2042,7 @@
         <v>20050</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" s="5">
         <v>3001003</v>
@@ -2041,16 +2054,16 @@
         <v>35</v>
       </c>
       <c r="G13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" t="s">
         <v>44</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>45</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>46</v>
-      </c>
-      <c r="J13" t="s">
-        <v>47</v>
       </c>
       <c r="K13">
         <v>4000</v>
@@ -2059,7 +2072,7 @@
         <v>8000</v>
       </c>
       <c r="M13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N13">
         <v>8000</v>
@@ -2073,7 +2086,7 @@
         <v>20025</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" s="5">
         <v>3001001</v>
@@ -2085,16 +2098,16 @@
         <v>28</v>
       </c>
       <c r="G14" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" t="s">
         <v>50</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" t="s">
         <v>51</v>
-      </c>
-      <c r="I14" t="s">
-        <v>52</v>
-      </c>
-      <c r="J14" t="s">
-        <v>53</v>
       </c>
       <c r="K14">
         <v>2000</v>
@@ -2103,7 +2116,7 @@
         <v>6000</v>
       </c>
       <c r="M14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N14">
         <v>6000</v>
@@ -2117,7 +2130,7 @@
         <v>20025</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" s="5">
         <v>3001002</v>
@@ -2129,16 +2142,16 @@
         <v>34</v>
       </c>
       <c r="G15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I15" t="s">
         <v>50</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" t="s">
         <v>51</v>
-      </c>
-      <c r="I15" t="s">
-        <v>52</v>
-      </c>
-      <c r="J15" t="s">
-        <v>53</v>
       </c>
       <c r="K15">
         <v>2000</v>
@@ -2147,7 +2160,7 @@
         <v>6000</v>
       </c>
       <c r="M15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N15">
         <v>6000</v>
@@ -2161,7 +2174,7 @@
         <v>20025</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" s="5">
         <v>3001003</v>
@@ -2173,16 +2186,16 @@
         <v>35</v>
       </c>
       <c r="G16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" t="s">
         <v>50</v>
       </c>
-      <c r="H16" t="s">
+      <c r="J16" t="s">
         <v>51</v>
-      </c>
-      <c r="I16" t="s">
-        <v>52</v>
-      </c>
-      <c r="J16" t="s">
-        <v>53</v>
       </c>
       <c r="K16">
         <v>2000</v>
@@ -2191,7 +2204,7 @@
         <v>6000</v>
       </c>
       <c r="M16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N16">
         <v>6000</v>
@@ -2205,7 +2218,7 @@
         <v>20001</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D17" s="5">
         <v>3001001</v>
@@ -2217,16 +2230,16 @@
         <v>28</v>
       </c>
       <c r="G17" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="H17" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I17" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K17">
         <v>1000</v>
@@ -2235,7 +2248,7 @@
         <v>4000</v>
       </c>
       <c r="M17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N17">
         <v>4000</v>
@@ -2249,7 +2262,7 @@
         <v>20001</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D18" s="5">
         <v>3001002</v>
@@ -2261,16 +2274,16 @@
         <v>34</v>
       </c>
       <c r="G18" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="H18" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K18">
         <v>1000</v>
@@ -2279,7 +2292,7 @@
         <v>4000</v>
       </c>
       <c r="M18" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N18">
         <v>4000</v>
@@ -2293,7 +2306,7 @@
         <v>20001</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D19" s="5">
         <v>3001003</v>
@@ -2305,16 +2318,16 @@
         <v>35</v>
       </c>
       <c r="G19" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="H19" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I19" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K19">
         <v>1000</v>
@@ -2323,7 +2336,7 @@
         <v>4000</v>
       </c>
       <c r="M19" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N19">
         <v>4000</v>
@@ -2343,7 +2356,7 @@
         <v>3002001</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>28</v>
@@ -2387,7 +2400,7 @@
         <v>3002002</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>34</v>
@@ -2431,7 +2444,7 @@
         <v>3002003</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>35</v>
@@ -2475,22 +2488,22 @@
         <v>3002001</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G23" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" t="s">
         <v>37</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>38</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>39</v>
-      </c>
-      <c r="J23" t="s">
-        <v>40</v>
       </c>
       <c r="K23">
         <v>6000</v>
@@ -2499,7 +2512,7 @@
         <v>10000</v>
       </c>
       <c r="M23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N23">
         <v>10000</v>
@@ -2519,22 +2532,22 @@
         <v>3002002</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H24" t="s">
         <v>37</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>38</v>
       </c>
-      <c r="I24" t="s">
-        <v>39</v>
-      </c>
       <c r="J24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K24">
         <v>6000</v>
@@ -2543,7 +2556,7 @@
         <v>10000</v>
       </c>
       <c r="M24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N24">
         <v>10000</v>
@@ -2563,22 +2576,22 @@
         <v>3002003</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" t="s">
         <v>37</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>38</v>
       </c>
-      <c r="I25" t="s">
-        <v>39</v>
-      </c>
       <c r="J25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K25">
         <v>6000</v>
@@ -2587,7 +2600,7 @@
         <v>10000</v>
       </c>
       <c r="M25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N25">
         <v>10000</v>
@@ -2601,28 +2614,28 @@
         <v>20050</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D26" s="5">
         <v>3002001</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G26" t="s">
+        <v>43</v>
+      </c>
+      <c r="H26" t="s">
         <v>44</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>45</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>46</v>
-      </c>
-      <c r="J26" t="s">
-        <v>47</v>
       </c>
       <c r="K26">
         <v>4000</v>
@@ -2631,7 +2644,7 @@
         <v>8000</v>
       </c>
       <c r="M26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N26">
         <v>8000</v>
@@ -2645,28 +2658,28 @@
         <v>20050</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D27" s="5">
         <v>3002002</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G27" t="s">
+        <v>43</v>
+      </c>
+      <c r="H27" t="s">
         <v>44</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>45</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>46</v>
-      </c>
-      <c r="J27" t="s">
-        <v>47</v>
       </c>
       <c r="K27">
         <v>4000</v>
@@ -2675,7 +2688,7 @@
         <v>8000</v>
       </c>
       <c r="M27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N27">
         <v>8000</v>
@@ -2689,28 +2702,28 @@
         <v>20050</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D28" s="5">
         <v>3002003</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G28" t="s">
+        <v>43</v>
+      </c>
+      <c r="H28" t="s">
         <v>44</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>45</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>46</v>
-      </c>
-      <c r="J28" t="s">
-        <v>47</v>
       </c>
       <c r="K28">
         <v>4000</v>
@@ -2719,7 +2732,7 @@
         <v>8000</v>
       </c>
       <c r="M28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N28">
         <v>8000</v>
@@ -2733,28 +2746,28 @@
         <v>20025</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D29" s="5">
         <v>3002001</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G29" t="s">
+        <v>43</v>
+      </c>
+      <c r="H29" t="s">
+        <v>49</v>
+      </c>
+      <c r="I29" t="s">
         <v>50</v>
       </c>
-      <c r="H29" t="s">
+      <c r="J29" t="s">
         <v>51</v>
-      </c>
-      <c r="I29" t="s">
-        <v>52</v>
-      </c>
-      <c r="J29" t="s">
-        <v>53</v>
       </c>
       <c r="K29">
         <v>2000</v>
@@ -2763,7 +2776,7 @@
         <v>6000</v>
       </c>
       <c r="M29" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N29">
         <v>6000</v>
@@ -2777,28 +2790,28 @@
         <v>20025</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D30" s="5">
         <v>3002002</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G30" t="s">
+        <v>43</v>
+      </c>
+      <c r="H30" t="s">
+        <v>49</v>
+      </c>
+      <c r="I30" t="s">
         <v>50</v>
       </c>
-      <c r="H30" t="s">
+      <c r="J30" t="s">
         <v>51</v>
-      </c>
-      <c r="I30" t="s">
-        <v>52</v>
-      </c>
-      <c r="J30" t="s">
-        <v>53</v>
       </c>
       <c r="K30">
         <v>2000</v>
@@ -2807,7 +2820,7 @@
         <v>6000</v>
       </c>
       <c r="M30" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N30">
         <v>6000</v>
@@ -2821,28 +2834,28 @@
         <v>20025</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D31" s="5">
         <v>3002003</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G31" t="s">
+        <v>43</v>
+      </c>
+      <c r="H31" t="s">
+        <v>49</v>
+      </c>
+      <c r="I31" t="s">
         <v>50</v>
       </c>
-      <c r="H31" t="s">
+      <c r="J31" t="s">
         <v>51</v>
-      </c>
-      <c r="I31" t="s">
-        <v>52</v>
-      </c>
-      <c r="J31" t="s">
-        <v>53</v>
       </c>
       <c r="K31">
         <v>2000</v>
@@ -2851,7 +2864,7 @@
         <v>6000</v>
       </c>
       <c r="M31" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N31">
         <v>6000</v>
@@ -2865,28 +2878,28 @@
         <v>20001</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D32" s="5">
         <v>3002001</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G32" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="H32" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I32" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J32" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K32">
         <v>1000</v>
@@ -2895,7 +2908,7 @@
         <v>4000</v>
       </c>
       <c r="M32" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N32">
         <v>4000</v>
@@ -2909,28 +2922,28 @@
         <v>20001</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D33" s="5">
         <v>3002002</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G33" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="H33" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I33" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J33" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K33">
         <v>1000</v>
@@ -2939,7 +2952,7 @@
         <v>4000</v>
       </c>
       <c r="M33" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N33">
         <v>4000</v>
@@ -2953,28 +2966,28 @@
         <v>20001</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D34" s="5">
         <v>3002003</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G34" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="H34" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I34" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J34" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K34">
         <v>1000</v>
@@ -2983,7 +2996,7 @@
         <v>4000</v>
       </c>
       <c r="M34" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N34">
         <v>4000</v>
